--- a/results/simulation/tables/supp_table_mutation_coverage_matrix.xlsx
+++ b/results/simulation/tables/supp_table_mutation_coverage_matrix.xlsx
@@ -447,10 +447,10 @@
         <v>25</v>
       </c>
       <c r="F1" s="1" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G1" s="1" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="2">
